--- a/Assets/Data/Excel/WaveConfig.xlsx
+++ b/Assets/Data/Excel/WaveConfig.xlsx
@@ -8,15 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEAF187-6B93-4A8D-8A80-E32C86120D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6512F317-3F12-4519-99AA-BC7AC46D2970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17520" yWindow="4980" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
-    <sheet name="Waves" sheetId="2" r:id="rId2"/>
-    <sheet name="MonsterPoints" sheetId="3" r:id="rId3"/>
-    <sheet name="RandomMonsterPoints" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,27 +28,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
-  <si>
-    <t>levelTag</t>
-  </si>
-  <si>
-    <t>levelName</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>第一关</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>第二关</t>
-  </si>
-  <si>
-    <t>levelWave</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+  <si>
+    <t>WaveId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>BigWave</t>
+  </si>
+  <si>
+    <t>MaxMonsterCap</t>
+  </si>
+  <si>
+    <t>RandomSpawnCD</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>唯一大波次ID</t>
+  </si>
+  <si>
+    <t>关卡号</t>
+  </si>
+  <si>
+    <t>大波次号</t>
+  </si>
+  <si>
+    <t>怪物最大上限</t>
+  </si>
+  <si>
+    <t>随机池内置CD</t>
   </si>
 </sst>
 </file>
@@ -74,7 +87,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -118,10 +130,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -406,35 +421,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>101</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2">
         <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -442,71 +501,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DFCAB0F-1B44-420C-B9DD-28E58FC393F6}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BCBBE3-EE51-4D2E-BCAC-7E829E59761E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8C2D00-72EB-4113-BE78-724FD8007514}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Assets/Data/Excel/WaveConfig.xlsx
+++ b/Assets/Data/Excel/WaveConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6512F317-3F12-4519-99AA-BC7AC46D2970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB844540-1CFC-4462-82E7-D11408F5AD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17520" yWindow="4980" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7830" yWindow="4320" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
@@ -424,8 +424,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
     <col min="2" max="2" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -462,7 +464,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>

--- a/Assets/Data/Excel/WaveConfig.xlsx
+++ b/Assets/Data/Excel/WaveConfig.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB844540-1CFC-4462-82E7-D11408F5AD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A9EDE7-4EB9-47D3-BAA0-052F2DF7E2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7830" yWindow="4320" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7050" yWindow="3840" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -28,10 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>WaveId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Level</t>
@@ -40,6 +36,9 @@
     <t>BigWave</t>
   </si>
   <si>
+    <t>Duration</t>
+  </si>
+  <si>
     <t>MaxMonsterCap</t>
   </si>
   <si>
@@ -59,6 +58,9 @@
   </si>
   <si>
     <t>大波次号</t>
+  </si>
+  <si>
+    <t>波次持续时间(秒)</t>
   </si>
   <si>
     <t>怪物最大上限</t>
@@ -130,16 +132,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -421,80 +426,174 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="4" max="4" width="19.25" customWidth="1"/>
-    <col min="5" max="5" width="18.125" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9" style="4"/>
+    <col min="4" max="4" width="19.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="18.125" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>101</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="4">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3">
         <v>7</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>102</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4">
+        <v>7</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>103</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>104</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4">
+        <v>30</v>
+      </c>
+      <c r="E7" s="4">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>105</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4">
+        <v>30</v>
+      </c>
+      <c r="E8" s="4">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4">
         <v>2</v>
       </c>
     </row>

--- a/Assets/Data/Excel/WaveConfig.xlsx
+++ b/Assets/Data/Excel/WaveConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A9EDE7-4EB9-47D3-BAA0-052F2DF7E2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A938E1B3-BCD3-4D51-93EE-E091AFBE56CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7050" yWindow="3840" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8610" yWindow="6300" windowWidth="13380" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Levels" sheetId="1" r:id="rId1"/>
@@ -508,13 +508,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
